--- a/data/raw/LM2020.xlsx
+++ b/data/raw/LM2020.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC333671-56F1-4352-A6BD-9BE425DE4387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92F1FB3-9097-4B1B-9DFD-D596C1896EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16485" windowWidth="29040" windowHeight="15720" tabRatio="913" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="913" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introducción" sheetId="47" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4294,11 +4294,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2CAAE0-71CA-4740-A6B8-7A4F101516B6}">
   <dimension ref="C1:E52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
-    <col min="4" max="4" width="67.140625" customWidth="1"/>
+    <col min="1" max="2" width="3.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
+    <col min="4" max="4" width="67.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:5">
@@ -4370,7 +4370,7 @@
       <c r="C18" s="103"/>
       <c r="D18" s="104"/>
     </row>
-    <row r="19" spans="3:4" ht="15.75">
+    <row r="19" spans="3:4" ht="15.6">
       <c r="C19" s="105"/>
       <c r="D19" s="104"/>
     </row>
@@ -4395,7 +4395,7 @@
     <row r="27" spans="3:4">
       <c r="C27" s="103"/>
     </row>
-    <row r="28" spans="3:4" ht="15.75">
+    <row r="28" spans="3:4" ht="15.6">
       <c r="C28" s="105"/>
     </row>
     <row r="29" spans="3:4">
@@ -4407,7 +4407,7 @@
     <row r="31" spans="3:4">
       <c r="C31" s="103"/>
     </row>
-    <row r="32" spans="3:4" ht="15.75">
+    <row r="32" spans="3:4" ht="15.6">
       <c r="C32" s="105"/>
     </row>
     <row r="33" spans="3:3">
@@ -4422,7 +4422,7 @@
     <row r="36" spans="3:3">
       <c r="C36" s="103"/>
     </row>
-    <row r="37" spans="3:3" ht="15.75">
+    <row r="37" spans="3:3" ht="15.6">
       <c r="C37" s="105"/>
     </row>
     <row r="38" spans="3:3">
@@ -4437,7 +4437,7 @@
     <row r="41" spans="3:3">
       <c r="C41" s="108"/>
     </row>
-    <row r="42" spans="3:3" ht="15.75">
+    <row r="42" spans="3:3" ht="15.6">
       <c r="C42" s="105"/>
     </row>
     <row r="43" spans="3:3">
@@ -4449,7 +4449,7 @@
     <row r="45" spans="3:3">
       <c r="C45" s="109"/>
     </row>
-    <row r="46" spans="3:3" ht="15.75">
+    <row r="46" spans="3:3" ht="15.6">
       <c r="C46" s="105"/>
     </row>
     <row r="47" spans="3:3">
@@ -4464,7 +4464,7 @@
     <row r="50" spans="3:3">
       <c r="C50" s="103"/>
     </row>
-    <row r="51" spans="3:3" ht="15.75">
+    <row r="51" spans="3:3" ht="15.6">
       <c r="C51" s="105"/>
     </row>
     <row r="52" spans="3:3">
@@ -4486,24 +4486,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AH866"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="12.85546875" style="6" customWidth="1"/>
-    <col min="6" max="16" width="12.85546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="12.88671875" style="6" customWidth="1"/>
+    <col min="6" max="16" width="12.88671875" style="3" customWidth="1"/>
     <col min="17" max="17" width="11" style="3" customWidth="1"/>
-    <col min="18" max="18" width="31.140625" style="3" customWidth="1"/>
-    <col min="19" max="33" width="12.85546875" style="3" customWidth="1"/>
-    <col min="34" max="34" width="15.7109375" style="3" customWidth="1"/>
-    <col min="35" max="35" width="25.7109375" style="3" customWidth="1"/>
-    <col min="36" max="36" width="17.140625" style="3" customWidth="1"/>
-    <col min="37" max="37" width="16.85546875" style="3" customWidth="1"/>
-    <col min="38" max="39" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="51" width="15.7109375" style="3" customWidth="1"/>
-    <col min="52" max="16384" width="33.140625" style="3"/>
+    <col min="18" max="18" width="31.109375" style="3" customWidth="1"/>
+    <col min="19" max="33" width="12.88671875" style="3" customWidth="1"/>
+    <col min="34" max="34" width="15.6640625" style="3" customWidth="1"/>
+    <col min="35" max="35" width="25.6640625" style="3" customWidth="1"/>
+    <col min="36" max="36" width="17.109375" style="3" customWidth="1"/>
+    <col min="37" max="37" width="16.88671875" style="3" customWidth="1"/>
+    <col min="38" max="39" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="51" width="15.6640625" style="3" customWidth="1"/>
+    <col min="52" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>142</v>
       </c>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="14.25">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="33" t="s">
         <v>453</v>
       </c>
@@ -4792,7 +4792,7 @@
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
     </row>
-    <row r="25" spans="1:34" ht="51">
+    <row r="25" spans="1:34" ht="55.2">
       <c r="A25" s="26" t="s">
         <v>50</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="V33" s="6"/>
       <c r="W33" s="6"/>
     </row>
-    <row r="34" spans="1:34" ht="51">
+    <row r="34" spans="1:34" ht="55.2">
       <c r="A34" s="15" t="s">
         <v>51</v>
       </c>
@@ -6441,7 +6441,7 @@
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
     </row>
-    <row r="48" spans="1:34" ht="51">
+    <row r="48" spans="1:34" ht="55.2">
       <c r="A48" s="15" t="s">
         <v>145</v>
       </c>
@@ -8469,7 +8469,7 @@
       <c r="V73" s="12"/>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="1:34" ht="14.25">
+    <row r="74" spans="1:34" ht="15.6">
       <c r="A74" s="33" t="s">
         <v>453</v>
       </c>
@@ -8772,7 +8772,7 @@
       <c r="V90" s="6"/>
       <c r="W90" s="6"/>
     </row>
-    <row r="91" spans="1:34" ht="51">
+    <row r="91" spans="1:34" ht="55.2">
       <c r="A91" s="26" t="s">
         <v>50</v>
       </c>
@@ -9344,7 +9344,7 @@
       <c r="V99" s="6"/>
       <c r="W99" s="6"/>
     </row>
-    <row r="100" spans="1:34" ht="51">
+    <row r="100" spans="1:34" ht="55.2">
       <c r="A100" s="15" t="s">
         <v>51</v>
       </c>
@@ -10416,7 +10416,7 @@
       <c r="V113" s="6"/>
       <c r="W113" s="6"/>
     </row>
-    <row r="114" spans="1:34" ht="51">
+    <row r="114" spans="1:34" ht="55.2">
       <c r="A114" s="15" t="s">
         <v>145</v>
       </c>
@@ -12551,23 +12551,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="12.85546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="12.88671875" style="6" customWidth="1"/>
     <col min="7" max="7" width="14" style="3" customWidth="1"/>
     <col min="8" max="8" width="30" style="3" customWidth="1"/>
-    <col min="9" max="9" width="31.140625" style="3" customWidth="1"/>
-    <col min="10" max="13" width="12.85546875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" style="3" customWidth="1"/>
+    <col min="10" max="13" width="12.88671875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.44140625" style="3" customWidth="1"/>
     <col min="16" max="16" width="14" style="3" customWidth="1"/>
     <col min="17" max="17" width="11" style="3" customWidth="1"/>
-    <col min="18" max="34" width="15.7109375" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="33.140625" style="3"/>
+    <col min="18" max="34" width="15.6640625" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75">
+    <row r="1" spans="1:17" ht="18">
       <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
@@ -12600,7 +12600,7 @@
       <c r="O4" s="55"/>
       <c r="Q4" s="55"/>
     </row>
-    <row r="5" spans="1:17" ht="14.25">
+    <row r="5" spans="1:17" ht="16.2">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -12762,7 +12762,7 @@
       <c r="O15" s="55"/>
       <c r="Q15" s="55"/>
     </row>
-    <row r="16" spans="1:17" ht="14.25">
+    <row r="16" spans="1:17" ht="16.2">
       <c r="A16" s="8" t="s">
         <v>49</v>
       </c>
@@ -12927,7 +12927,7 @@
       <c r="O26" s="55"/>
       <c r="Q26" s="55"/>
     </row>
-    <row r="27" spans="1:19" ht="14.25">
+    <row r="27" spans="1:19" ht="16.2">
       <c r="A27" s="8" t="s">
         <v>144</v>
       </c>
@@ -12984,7 +12984,7 @@
       <c r="Q29" s="55"/>
       <c r="S29" s="55"/>
     </row>
-    <row r="30" spans="1:19" ht="14.25">
+    <row r="30" spans="1:19" ht="15.6">
       <c r="A30" s="22" t="s">
         <v>457</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="14.25">
+    <row r="48" spans="1:19" ht="16.2">
       <c r="A48" s="34" t="s">
         <v>419</v>
       </c>
@@ -13388,7 +13388,7 @@
       </c>
       <c r="N51" s="49"/>
     </row>
-    <row r="52" spans="1:14" ht="14.25">
+    <row r="52" spans="1:14" ht="15.6">
       <c r="A52" s="22" t="s">
         <v>455</v>
       </c>
@@ -13915,17 +13915,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25DD2BDE-3845-3249-809D-ADA5317011A8}">
   <dimension ref="A1:M64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2" max="4" width="14.85546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="3" customWidth="1"/>
+    <col min="2" max="4" width="14.88671875" style="6" customWidth="1"/>
     <col min="5" max="5" width="13" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="3" customWidth="1"/>
-    <col min="9" max="11" width="6.42578125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="33.140625" style="3"/>
+    <col min="6" max="8" width="8.88671875" style="3" customWidth="1"/>
+    <col min="9" max="11" width="6.44140625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="1" t="s">
         <v>458</v>
       </c>
@@ -14580,21 +14580,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N824"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="12.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="47" customWidth="1"/>
-    <col min="8" max="8" width="31.140625" style="3" customWidth="1"/>
-    <col min="9" max="10" width="12.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" style="48" customWidth="1"/>
-    <col min="15" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="31.109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="12.88671875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="31.109375" style="3" customWidth="1"/>
+    <col min="9" max="10" width="12.88671875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" style="48" customWidth="1"/>
+    <col min="15" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75">
+    <row r="1" spans="1:14" ht="18">
       <c r="A1" s="1" t="s">
         <v>213</v>
       </c>
@@ -14644,7 +14644,7 @@
       <c r="E6" s="46"/>
       <c r="F6" s="46"/>
     </row>
-    <row r="7" spans="1:14" ht="12.75">
+    <row r="7" spans="1:14" ht="13.8">
       <c r="A7" s="16" t="s">
         <v>29</v>
       </c>
@@ -14661,7 +14661,7 @@
       <c r="F7" s="46"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="12.75">
+    <row r="8" spans="1:14" ht="13.8">
       <c r="A8" s="16" t="s">
         <v>4</v>
       </c>
@@ -14678,7 +14678,7 @@
       <c r="F8" s="46"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="12.75">
+    <row r="9" spans="1:14" ht="13.8">
       <c r="A9" s="16" t="s">
         <v>216</v>
       </c>
@@ -14695,7 +14695,7 @@
       <c r="F9" s="46"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="12.75">
+    <row r="10" spans="1:14" ht="13.8">
       <c r="A10" s="20" t="s">
         <v>46</v>
       </c>
@@ -14712,7 +14712,7 @@
       <c r="F10" s="46"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="12.75">
+    <row r="11" spans="1:14" ht="13.8">
       <c r="B11" s="46"/>
       <c r="C11" s="46"/>
       <c r="D11" s="46"/>
@@ -14720,7 +14720,7 @@
       <c r="F11" s="47"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="12.75">
+    <row r="13" spans="1:14" ht="13.8">
       <c r="A13" s="7" t="s">
         <v>200</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="12.75">
+    <row r="14" spans="1:14" ht="13.8">
       <c r="A14" s="7" t="s">
         <v>426</v>
       </c>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="25.5">
+    <row r="15" spans="1:14" ht="41.4">
       <c r="A15" s="26" t="s">
         <v>50</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="12.75">
+    <row r="16" spans="1:14" ht="13.8">
       <c r="A16" s="13" t="s">
         <v>5</v>
       </c>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="N16" s="49"/>
     </row>
-    <row r="17" spans="1:14" ht="12.75">
+    <row r="17" spans="1:14" ht="13.8">
       <c r="A17" s="16" t="s">
         <v>6</v>
       </c>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="N17" s="49"/>
     </row>
-    <row r="18" spans="1:14" ht="12.75">
+    <row r="18" spans="1:14" ht="13.8">
       <c r="A18" s="22" t="s">
         <v>216</v>
       </c>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="N18" s="49"/>
     </row>
-    <row r="19" spans="1:14" ht="12.75">
+    <row r="19" spans="1:14" ht="13.8">
       <c r="A19" s="20" t="s">
         <v>46</v>
       </c>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="N19" s="49"/>
     </row>
-    <row r="20" spans="1:14" ht="12.75">
+    <row r="20" spans="1:14" ht="13.8">
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -14950,7 +14950,7 @@
       <c r="L20" s="53"/>
       <c r="M20" s="53"/>
     </row>
-    <row r="21" spans="1:14" ht="12.75">
+    <row r="21" spans="1:14" ht="13.8">
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="46"/>
@@ -14960,7 +14960,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="12.75">
+    <row r="22" spans="1:14" ht="13.8">
       <c r="A22" s="7" t="s">
         <v>202</v>
       </c>
@@ -14976,7 +14976,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="12.75">
+    <row r="23" spans="1:14" ht="13.8">
       <c r="A23" s="7" t="s">
         <v>427</v>
       </c>
@@ -14992,7 +14992,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="25.5">
+    <row r="24" spans="1:14" ht="41.4">
       <c r="A24" s="15" t="s">
         <v>51</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="12.75">
+    <row r="25" spans="1:14" ht="13.8">
       <c r="A25" s="13" t="s">
         <v>40</v>
       </c>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="N25" s="49"/>
     </row>
-    <row r="26" spans="1:14" ht="12.75">
+    <row r="26" spans="1:14" ht="13.8">
       <c r="A26" s="16" t="s">
         <v>2</v>
       </c>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="N26" s="49"/>
     </row>
-    <row r="27" spans="1:14" ht="12.75">
+    <row r="27" spans="1:14" ht="13.8">
       <c r="A27" s="16" t="s">
         <v>41</v>
       </c>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="N27" s="49"/>
     </row>
-    <row r="28" spans="1:14" ht="12.75">
+    <row r="28" spans="1:14" ht="13.8">
       <c r="A28" s="16" t="s">
         <v>42</v>
       </c>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="N28" s="49"/>
     </row>
-    <row r="29" spans="1:14" ht="12.75">
+    <row r="29" spans="1:14" ht="13.8">
       <c r="A29" s="16" t="s">
         <v>43</v>
       </c>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="N29" s="49"/>
     </row>
-    <row r="30" spans="1:14" ht="12.75">
+    <row r="30" spans="1:14" ht="13.8">
       <c r="A30" s="16" t="s">
         <v>44</v>
       </c>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="N30" s="49"/>
     </row>
-    <row r="31" spans="1:14" ht="12.75">
+    <row r="31" spans="1:14" ht="13.8">
       <c r="A31" s="16" t="s">
         <v>3</v>
       </c>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="N31" s="49"/>
     </row>
-    <row r="32" spans="1:14" ht="12.75">
+    <row r="32" spans="1:14" ht="13.8">
       <c r="A32" s="22" t="s">
         <v>216</v>
       </c>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="N32" s="49"/>
     </row>
-    <row r="33" spans="1:14" ht="12.75">
+    <row r="33" spans="1:14" ht="13.8">
       <c r="A33" s="20" t="s">
         <v>46</v>
       </c>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="N33" s="49"/>
     </row>
-    <row r="34" spans="1:14" ht="12.75">
+    <row r="34" spans="1:14" ht="13.8">
       <c r="B34" s="46"/>
       <c r="C34" s="46"/>
       <c r="D34" s="46"/>
@@ -15404,7 +15404,7 @@
       <c r="L34" s="46"/>
       <c r="M34" s="46"/>
     </row>
-    <row r="35" spans="1:14" ht="12.75">
+    <row r="35" spans="1:14" ht="13.8">
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="46"/>
@@ -15414,7 +15414,7 @@
       <c r="L35" s="6"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="12.75">
+    <row r="36" spans="1:14" ht="13.8">
       <c r="A36" s="7" t="s">
         <v>204</v>
       </c>
@@ -15430,7 +15430,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="12.75">
+    <row r="37" spans="1:14" ht="13.8">
       <c r="A37" s="7" t="s">
         <v>428</v>
       </c>
@@ -15446,7 +15446,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="25.5">
+    <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="8" t="s">
         <v>144</v>
       </c>
@@ -15485,7 +15485,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="12.75">
+    <row r="39" spans="1:14" ht="13.8">
       <c r="A39" s="22" t="s">
         <v>9</v>
       </c>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="N39" s="49"/>
     </row>
-    <row r="40" spans="1:14" ht="12.75">
+    <row r="40" spans="1:14" ht="13.8">
       <c r="A40" s="22" t="s">
         <v>10</v>
       </c>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="N40" s="49"/>
     </row>
-    <row r="41" spans="1:14" ht="14.25">
+    <row r="41" spans="1:14" ht="15.6">
       <c r="A41" s="22" t="s">
         <v>453</v>
       </c>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="N41" s="49"/>
     </row>
-    <row r="42" spans="1:14" ht="12.75">
+    <row r="42" spans="1:14" ht="13.8">
       <c r="A42" s="22" t="s">
         <v>11</v>
       </c>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="N42" s="49"/>
     </row>
-    <row r="43" spans="1:14" ht="12.75">
+    <row r="43" spans="1:14" ht="13.8">
       <c r="A43" s="22" t="s">
         <v>12</v>
       </c>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="N43" s="49"/>
     </row>
-    <row r="44" spans="1:14" ht="12.75">
+    <row r="44" spans="1:14" ht="13.8">
       <c r="A44" s="22" t="s">
         <v>13</v>
       </c>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="N44" s="49"/>
     </row>
-    <row r="45" spans="1:14" ht="12.75">
+    <row r="45" spans="1:14" ht="13.8">
       <c r="A45" s="22" t="s">
         <v>159</v>
       </c>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="N45" s="49"/>
     </row>
-    <row r="46" spans="1:14" ht="12.75">
+    <row r="46" spans="1:14" ht="13.8">
       <c r="A46" s="22" t="s">
         <v>349</v>
       </c>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="N46" s="49"/>
     </row>
-    <row r="47" spans="1:14" ht="12.75">
+    <row r="47" spans="1:14" ht="13.8">
       <c r="A47" s="22" t="s">
         <v>197</v>
       </c>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="N47" s="49"/>
     </row>
-    <row r="48" spans="1:14" ht="12.75">
+    <row r="48" spans="1:14" ht="13.8">
       <c r="A48" s="22" t="s">
         <v>162</v>
       </c>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="N48" s="49"/>
     </row>
-    <row r="49" spans="1:14" ht="12.75">
+    <row r="49" spans="1:14" ht="13.8">
       <c r="A49" s="22" t="s">
         <v>161</v>
       </c>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="N49" s="49"/>
     </row>
-    <row r="50" spans="1:14" ht="12.75">
+    <row r="50" spans="1:14" ht="13.8">
       <c r="A50" s="22" t="s">
         <v>160</v>
       </c>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="N50" s="49"/>
     </row>
-    <row r="51" spans="1:14" ht="12.75">
+    <row r="51" spans="1:14" ht="13.8">
       <c r="A51" s="22" t="s">
         <v>31</v>
       </c>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="N51" s="49"/>
     </row>
-    <row r="52" spans="1:14" ht="12.75">
+    <row r="52" spans="1:14" ht="13.8">
       <c r="A52" s="22" t="s">
         <v>216</v>
       </c>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="N52" s="49"/>
     </row>
-    <row r="53" spans="1:14" ht="12.75">
+    <row r="53" spans="1:14" ht="13.8">
       <c r="A53" s="20" t="s">
         <v>46</v>
       </c>
@@ -16084,7 +16084,7 @@
         <v>1338666</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="27.95" customHeight="1">
+    <row r="54" spans="1:14" ht="27.9" customHeight="1">
       <c r="A54" s="131" t="s">
         <v>402</v>
       </c>
@@ -16103,7 +16103,7 @@
       <c r="L54" s="131"/>
       <c r="M54" s="131"/>
     </row>
-    <row r="55" spans="1:14" ht="12.75">
+    <row r="55" spans="1:14" ht="13.8">
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="48"/>
@@ -16113,7 +16113,7 @@
       <c r="L55" s="6"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="12.75">
+    <row r="56" spans="1:14" ht="13.8">
       <c r="A56" s="7" t="s">
         <v>206</v>
       </c>
@@ -16125,7 +16125,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="12.75">
+    <row r="57" spans="1:14" ht="13.8">
       <c r="A57" s="7" t="s">
         <v>328</v>
       </c>
@@ -16138,7 +16138,7 @@
       <c r="K57" s="3"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="12.75">
+    <row r="58" spans="1:14" ht="13.8">
       <c r="A58" s="8" t="s">
         <v>169</v>
       </c>
@@ -16159,7 +16159,7 @@
       <c r="L58" s="25"/>
       <c r="M58" s="25"/>
     </row>
-    <row r="59" spans="1:14" ht="12.75">
+    <row r="59" spans="1:14" ht="13.8">
       <c r="A59" s="16" t="s">
         <v>30</v>
       </c>
@@ -16180,7 +16180,7 @@
       <c r="L59" s="12"/>
       <c r="M59" s="12"/>
     </row>
-    <row r="60" spans="1:14" ht="12.75">
+    <row r="60" spans="1:14" ht="13.8">
       <c r="A60" s="16" t="s">
         <v>29</v>
       </c>
@@ -16201,7 +16201,7 @@
       <c r="L60" s="12"/>
       <c r="M60" s="12"/>
     </row>
-    <row r="61" spans="1:14" ht="12.75">
+    <row r="61" spans="1:14" ht="13.8">
       <c r="A61" s="16" t="s">
         <v>4</v>
       </c>
@@ -16222,7 +16222,7 @@
       <c r="L61" s="12"/>
       <c r="M61" s="12"/>
     </row>
-    <row r="62" spans="1:14" ht="12.75">
+    <row r="62" spans="1:14" ht="13.8">
       <c r="A62" s="16" t="s">
         <v>216</v>
       </c>
@@ -16243,7 +16243,7 @@
       <c r="L62" s="12"/>
       <c r="M62" s="12"/>
     </row>
-    <row r="63" spans="1:14" ht="12.75">
+    <row r="63" spans="1:14" ht="13.8">
       <c r="A63" s="20" t="s">
         <v>46</v>
       </c>
@@ -16264,7 +16264,7 @@
       <c r="L63" s="12"/>
       <c r="M63" s="12"/>
     </row>
-    <row r="64" spans="1:14" ht="12.75">
+    <row r="64" spans="1:14" ht="13.8">
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
@@ -16274,7 +16274,7 @@
       <c r="K64" s="3"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="12.75">
+    <row r="65" spans="1:14" ht="13.8">
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="48"/>
@@ -16284,7 +16284,7 @@
       <c r="L65" s="6"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:14" ht="12.75">
+    <row r="66" spans="1:14" ht="13.8">
       <c r="A66" s="7" t="s">
         <v>207</v>
       </c>
@@ -16300,7 +16300,7 @@
       <c r="L66" s="6"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:14" ht="12.75">
+    <row r="67" spans="1:14" ht="13.8">
       <c r="A67" s="7" t="s">
         <v>429</v>
       </c>
@@ -16316,7 +16316,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:14" ht="25.5">
+    <row r="68" spans="1:14" ht="41.4">
       <c r="A68" s="26" t="s">
         <v>50</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="12.75">
+    <row r="69" spans="1:14" ht="13.8">
       <c r="A69" s="13" t="s">
         <v>5</v>
       </c>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="N69" s="49"/>
     </row>
-    <row r="70" spans="1:14" ht="12.75">
+    <row r="70" spans="1:14" ht="13.8">
       <c r="A70" s="16" t="s">
         <v>6</v>
       </c>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="N70" s="49"/>
     </row>
-    <row r="71" spans="1:14" ht="12.75">
+    <row r="71" spans="1:14" ht="13.8">
       <c r="A71" s="22" t="s">
         <v>216</v>
       </c>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="N71" s="49"/>
     </row>
-    <row r="72" spans="1:14" ht="12.75">
+    <row r="72" spans="1:14" ht="13.8">
       <c r="A72" s="20" t="s">
         <v>46</v>
       </c>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="N72" s="49"/>
     </row>
-    <row r="73" spans="1:14" ht="12.75">
+    <row r="73" spans="1:14" ht="13.8">
       <c r="B73" s="46"/>
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
@@ -16528,7 +16528,7 @@
       <c r="L73" s="52"/>
       <c r="M73" s="49"/>
     </row>
-    <row r="74" spans="1:14" ht="12.75">
+    <row r="74" spans="1:14" ht="13.8">
       <c r="D74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="48"/>
@@ -16538,7 +16538,7 @@
       <c r="L74" s="6"/>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" spans="1:14" ht="12.75">
+    <row r="75" spans="1:14" ht="13.8">
       <c r="A75" s="7" t="s">
         <v>209</v>
       </c>
@@ -16554,7 +16554,7 @@
       <c r="L75" s="6"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:14" ht="12.75">
+    <row r="76" spans="1:14" ht="13.8">
       <c r="A76" s="7" t="s">
         <v>430</v>
       </c>
@@ -16570,7 +16570,7 @@
       <c r="L76" s="6"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:14" ht="25.5">
+    <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="15" t="s">
         <v>51</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="12.75">
+    <row r="78" spans="1:14" ht="13.8">
       <c r="A78" s="13" t="s">
         <v>40</v>
       </c>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N78" s="49"/>
     </row>
-    <row r="79" spans="1:14" ht="12.75">
+    <row r="79" spans="1:14" ht="13.8">
       <c r="A79" s="16" t="s">
         <v>2</v>
       </c>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="N79" s="49"/>
     </row>
-    <row r="80" spans="1:14" ht="12.75">
+    <row r="80" spans="1:14" ht="13.8">
       <c r="A80" s="16" t="s">
         <v>41</v>
       </c>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="N80" s="49"/>
     </row>
-    <row r="81" spans="1:14" ht="12.75">
+    <row r="81" spans="1:14" ht="13.8">
       <c r="A81" s="16" t="s">
         <v>42</v>
       </c>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="N81" s="49"/>
     </row>
-    <row r="82" spans="1:14" ht="12.75">
+    <row r="82" spans="1:14" ht="13.8">
       <c r="A82" s="16" t="s">
         <v>43</v>
       </c>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="N82" s="49"/>
     </row>
-    <row r="83" spans="1:14" ht="12.75">
+    <row r="83" spans="1:14" ht="13.8">
       <c r="A83" s="16" t="s">
         <v>44</v>
       </c>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="N83" s="49"/>
     </row>
-    <row r="84" spans="1:14" ht="12.75">
+    <row r="84" spans="1:14" ht="13.8">
       <c r="A84" s="16" t="s">
         <v>3</v>
       </c>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="N84" s="49"/>
     </row>
-    <row r="85" spans="1:14" ht="12.75">
+    <row r="85" spans="1:14" ht="13.8">
       <c r="A85" s="22" t="s">
         <v>216</v>
       </c>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="N85" s="49"/>
     </row>
-    <row r="86" spans="1:14" ht="12.75">
+    <row r="86" spans="1:14" ht="13.8">
       <c r="A86" s="20" t="s">
         <v>46</v>
       </c>
@@ -16969,7 +16969,7 @@
       </c>
       <c r="N86" s="49"/>
     </row>
-    <row r="87" spans="1:14" ht="12.75">
+    <row r="87" spans="1:14" ht="13.8">
       <c r="B87" s="46"/>
       <c r="C87" s="46"/>
       <c r="D87" s="46"/>
@@ -16982,7 +16982,7 @@
       <c r="L87" s="46"/>
       <c r="M87" s="46"/>
     </row>
-    <row r="88" spans="1:14" ht="12.75">
+    <row r="88" spans="1:14" ht="13.8">
       <c r="D88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="48"/>
@@ -16992,7 +16992,7 @@
       <c r="L88" s="6"/>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" spans="1:14" ht="12.75">
+    <row r="89" spans="1:14" ht="13.8">
       <c r="A89" s="7" t="s">
         <v>211</v>
       </c>
@@ -17008,7 +17008,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:14" ht="12.75">
+    <row r="90" spans="1:14" ht="13.8">
       <c r="A90" s="7" t="s">
         <v>431</v>
       </c>
@@ -17024,7 +17024,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:14" ht="25.5">
+    <row r="91" spans="1:14" ht="41.4">
       <c r="A91" s="8" t="s">
         <v>144</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="12.75">
+    <row r="92" spans="1:14" ht="13.8">
       <c r="A92" s="22" t="s">
         <v>9</v>
       </c>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="N92" s="49"/>
     </row>
-    <row r="93" spans="1:14" ht="12.75">
+    <row r="93" spans="1:14" ht="13.8">
       <c r="A93" s="22" t="s">
         <v>10</v>
       </c>
@@ -18204,10 +18204,10 @@
       <c r="K166" s="3"/>
       <c r="M166" s="3"/>
     </row>
-    <row r="801" spans="2:13" ht="12.75">
+    <row r="801" spans="2:13" ht="13.8">
       <c r="K801" s="3"/>
     </row>
-    <row r="802" spans="2:13" ht="12.75">
+    <row r="802" spans="2:13" ht="13.8">
       <c r="K802" s="3"/>
     </row>
     <row r="812" spans="2:13" ht="15" customHeight="1">
@@ -18355,19 +18355,19 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N840"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="13.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="47" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="3" customWidth="1"/>
-    <col min="9" max="12" width="13.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="48" customWidth="1"/>
-    <col min="15" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="29.109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="13.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="47" customWidth="1"/>
+    <col min="8" max="8" width="30.109375" style="3" customWidth="1"/>
+    <col min="9" max="12" width="13.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" style="48" customWidth="1"/>
+    <col min="15" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75">
+    <row r="1" spans="1:14" ht="18">
       <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25">
+    <row r="5" spans="1:14" ht="16.2">
       <c r="A5" s="8" t="s">
         <v>169</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14.25">
+    <row r="14" spans="1:14" ht="16.2">
       <c r="A14" s="7" t="s">
         <v>432</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="25.5">
+    <row r="15" spans="1:14" ht="27.6">
       <c r="A15" s="26" t="s">
         <v>50</v>
       </c>
@@ -18738,7 +18738,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="14.25">
+    <row r="23" spans="1:14" ht="16.2">
       <c r="A23" s="7" t="s">
         <v>433</v>
       </c>
@@ -18753,7 +18753,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="25.5">
+    <row r="24" spans="1:14" ht="27.6">
       <c r="A24" s="15" t="s">
         <v>51</v>
       </c>
@@ -19192,7 +19192,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="14.25">
+    <row r="37" spans="1:14" ht="16.2">
       <c r="A37" s="7" t="s">
         <v>434</v>
       </c>
@@ -19207,7 +19207,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="25.5">
+    <row r="38" spans="1:14" ht="27.6">
       <c r="A38" s="8" t="s">
         <v>144</v>
       </c>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="N40" s="49"/>
     </row>
-    <row r="41" spans="1:14" ht="14.25">
+    <row r="41" spans="1:14" ht="15.6">
       <c r="A41" s="22" t="s">
         <v>453</v>
       </c>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="N53" s="49"/>
     </row>
-    <row r="54" spans="1:14" ht="15.95" customHeight="1">
+    <row r="54" spans="1:14" ht="15.9" customHeight="1">
       <c r="A54" s="131" t="s">
         <v>402</v>
       </c>
@@ -19908,7 +19908,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="14.25">
+    <row r="58" spans="1:14" ht="16.2">
       <c r="A58" s="8" t="s">
         <v>169</v>
       </c>
@@ -20085,7 +20085,7 @@
       <c r="L66" s="6"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:14" ht="14.25">
+    <row r="67" spans="1:14" ht="16.2">
       <c r="A67" s="7" t="s">
         <v>435</v>
       </c>
@@ -20100,7 +20100,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:14" ht="25.5">
+    <row r="68" spans="1:14" ht="27.6">
       <c r="A68" s="26" t="s">
         <v>50</v>
       </c>
@@ -20338,7 +20338,7 @@
       <c r="L75" s="6"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:14" ht="14.25">
+    <row r="76" spans="1:14" ht="16.2">
       <c r="A76" s="7" t="s">
         <v>436</v>
       </c>
@@ -20353,7 +20353,7 @@
       <c r="L76" s="6"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:14" ht="25.5">
+    <row r="77" spans="1:14" ht="27.6">
       <c r="A77" s="15" t="s">
         <v>51</v>
       </c>
@@ -20792,7 +20792,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:14" ht="14.25">
+    <row r="90" spans="1:14" ht="16.2">
       <c r="A90" s="7" t="s">
         <v>437</v>
       </c>
@@ -20807,7 +20807,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:14" ht="25.5">
+    <row r="91" spans="1:14" ht="27.6">
       <c r="A91" s="8" t="s">
         <v>144</v>
       </c>
@@ -21464,7 +21464,7 @@
       <c r="L107" s="46"/>
       <c r="M107" s="46"/>
     </row>
-    <row r="108" spans="1:14" ht="30.95" customHeight="1">
+    <row r="108" spans="1:14" ht="30.9" customHeight="1">
       <c r="A108" s="130"/>
       <c r="B108" s="130"/>
       <c r="C108" s="130"/>
@@ -22198,21 +22198,21 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:V840"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="12.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="47" customWidth="1"/>
-    <col min="8" max="8" width="31.140625" style="3" customWidth="1"/>
-    <col min="9" max="12" width="12.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" style="48" customWidth="1"/>
-    <col min="15" max="18" width="13.85546875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="7.42578125" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="31.109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="12.88671875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="31.109375" style="3" customWidth="1"/>
+    <col min="9" max="12" width="12.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" style="48" customWidth="1"/>
+    <col min="15" max="18" width="13.88671875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="7.44140625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.75">
+    <row r="1" spans="1:22" ht="18">
       <c r="A1" s="1" t="s">
         <v>215</v>
       </c>
@@ -22411,7 +22411,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="25.5">
+    <row r="15" spans="1:22" ht="41.4">
       <c r="A15" s="26" t="s">
         <v>50</v>
       </c>
@@ -22659,7 +22659,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="25.5">
+    <row r="24" spans="1:14" ht="41.4">
       <c r="A24" s="15" t="s">
         <v>51</v>
       </c>
@@ -23110,7 +23110,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="25.5">
+    <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="8" t="s">
         <v>144</v>
       </c>
@@ -23229,7 +23229,7 @@
       </c>
       <c r="N40" s="49"/>
     </row>
-    <row r="41" spans="1:14" ht="14.25">
+    <row r="41" spans="1:14" ht="15.6">
       <c r="A41" s="22" t="s">
         <v>453</v>
       </c>
@@ -23976,7 +23976,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:14" ht="25.5">
+    <row r="68" spans="1:14" ht="41.4">
       <c r="A68" s="26" t="s">
         <v>50</v>
       </c>
@@ -24229,7 +24229,7 @@
       <c r="L76" s="6"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:14" ht="25.5">
+    <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="15" t="s">
         <v>51</v>
       </c>
@@ -24682,7 +24682,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:14" ht="25.5">
+    <row r="91" spans="1:14" ht="41.4">
       <c r="A91" s="8" t="s">
         <v>144</v>
       </c>
@@ -26057,9 +26057,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68072E5-4C97-F543-8047-E260534FF48D}">
   <dimension ref="A2:B190"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="142.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="142.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="18.75" customHeight="1">
@@ -26070,7 +26070,7 @@
     <row r="3" spans="1:2" ht="15" customHeight="1">
       <c r="B3" s="125"/>
     </row>
-    <row r="4" spans="1:2" ht="15.75">
+    <row r="4" spans="1:2" ht="15.6">
       <c r="B4" s="111" t="s">
         <v>74</v>
       </c>
@@ -26146,7 +26146,7 @@
     <row r="18" spans="1:2">
       <c r="B18" s="115"/>
     </row>
-    <row r="19" spans="1:2" ht="15.75">
+    <row r="19" spans="1:2" ht="15.6">
       <c r="B19" s="111" t="s">
         <v>137</v>
       </c>
@@ -26237,7 +26237,7 @@
     <row r="37" spans="2:2">
       <c r="B37" s="64"/>
     </row>
-    <row r="38" spans="2:2" ht="15.75">
+    <row r="38" spans="2:2" ht="15.6">
       <c r="B38" s="111" t="s">
         <v>138</v>
       </c>
@@ -26318,7 +26318,7 @@
     <row r="54" spans="2:2">
       <c r="B54" s="64"/>
     </row>
-    <row r="55" spans="2:2" ht="15.75">
+    <row r="55" spans="2:2" ht="15.6">
       <c r="B55" s="111" t="s">
         <v>139</v>
       </c>
@@ -26399,7 +26399,7 @@
     <row r="71" spans="2:2">
       <c r="B71" s="64"/>
     </row>
-    <row r="72" spans="2:2" ht="15.75">
+    <row r="72" spans="2:2" ht="15.6">
       <c r="B72" s="111" t="s">
         <v>480</v>
       </c>
@@ -26480,7 +26480,7 @@
     <row r="88" spans="2:2">
       <c r="B88" s="115"/>
     </row>
-    <row r="89" spans="2:2" ht="15.75">
+    <row r="89" spans="2:2" ht="15.6">
       <c r="B89" s="111" t="s">
         <v>481</v>
       </c>
@@ -26561,7 +26561,7 @@
     <row r="105" spans="2:2">
       <c r="B105" s="115"/>
     </row>
-    <row r="106" spans="2:2" ht="15.75">
+    <row r="106" spans="2:2" ht="15.6">
       <c r="B106" s="111" t="s">
         <v>482</v>
       </c>
@@ -26642,7 +26642,7 @@
     <row r="122" spans="2:2">
       <c r="B122" s="115"/>
     </row>
-    <row r="123" spans="2:2" ht="15.75">
+    <row r="123" spans="2:2" ht="15.6">
       <c r="B123" s="111" t="s">
         <v>483</v>
       </c>
@@ -26678,7 +26678,7 @@
     <row r="130" spans="2:2">
       <c r="B130" s="115"/>
     </row>
-    <row r="131" spans="2:2" ht="15.75">
+    <row r="131" spans="2:2" ht="15.6">
       <c r="B131" s="111" t="s">
         <v>484</v>
       </c>
@@ -26719,7 +26719,7 @@
     <row r="139" spans="2:2">
       <c r="B139" s="115"/>
     </row>
-    <row r="140" spans="2:2" ht="15.75">
+    <row r="140" spans="2:2" ht="15.6">
       <c r="B140" s="111" t="s">
         <v>213</v>
       </c>
@@ -26800,7 +26800,7 @@
     <row r="156" spans="2:2">
       <c r="B156" s="115"/>
     </row>
-    <row r="157" spans="2:2" ht="15.75">
+    <row r="157" spans="2:2" ht="15.6">
       <c r="B157" s="111" t="s">
         <v>214</v>
       </c>
@@ -26881,7 +26881,7 @@
     <row r="173" spans="2:2">
       <c r="B173" s="115"/>
     </row>
-    <row r="174" spans="2:2" ht="15.75">
+    <row r="174" spans="2:2" ht="15.6">
       <c r="B174" s="111" t="s">
         <v>215</v>
       </c>
@@ -27126,10 +27126,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B364AC1A-2160-9643-B8C1-6059C94CBA3D}">
   <dimension ref="B2:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="18.75" customHeight="1">
@@ -27142,7 +27142,7 @@
       <c r="B3" s="128"/>
       <c r="C3" s="129"/>
     </row>
-    <row r="4" spans="2:3" ht="18.75">
+    <row r="4" spans="2:3" ht="18">
       <c r="B4" s="59" t="s">
         <v>352</v>
       </c>
@@ -27329,24 +27329,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N137"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" style="3" customWidth="1"/>
-    <col min="9" max="12" width="11.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="15.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="27.42578125" style="3" customWidth="1"/>
-    <col min="20" max="39" width="15.7109375" style="3" customWidth="1"/>
-    <col min="40" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="12.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
+    <col min="5" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" style="3" customWidth="1"/>
+    <col min="9" max="12" width="11.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="27.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="15.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="27.44140625" style="3" customWidth="1"/>
+    <col min="20" max="39" width="15.6640625" style="3" customWidth="1"/>
+    <col min="40" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -28203,7 +28203,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="39">
+    <row r="72" spans="1:6" ht="41.4">
       <c r="A72" s="23" t="s">
         <v>238</v>
       </c>
@@ -28581,13 +28581,13 @@
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="15.75">
+    <row r="101" spans="1:13" ht="15.6">
       <c r="A101" s="2" t="s">
         <v>476</v>
       </c>
       <c r="H101" s="97"/>
     </row>
-    <row r="102" spans="1:13" ht="15.75">
+    <row r="102" spans="1:13" ht="15.6">
       <c r="A102" s="8" t="s">
         <v>49</v>
       </c>
@@ -28608,7 +28608,7 @@
       <c r="L102" s="92"/>
       <c r="M102" s="92"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75">
+    <row r="103" spans="1:13" ht="15.6">
       <c r="A103" s="16">
         <v>2016</v>
       </c>
@@ -28730,7 +28730,7 @@
       <c r="C109" s="32"/>
       <c r="E109" s="50"/>
     </row>
-    <row r="110" spans="1:13" ht="12.75">
+    <row r="110" spans="1:13" ht="13.8">
       <c r="A110" s="2" t="s">
         <v>148</v>
       </c>
@@ -28742,7 +28742,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="1:13" ht="12.75">
+    <row r="111" spans="1:13" ht="13.8">
       <c r="A111" s="9" t="s">
         <v>249</v>
       </c>
@@ -28754,7 +28754,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
     </row>
-    <row r="112" spans="1:13" ht="38.25">
+    <row r="112" spans="1:13" ht="41.4">
       <c r="A112" s="26" t="s">
         <v>238</v>
       </c>
@@ -28789,7 +28789,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="12.75">
+    <row r="113" spans="1:14" ht="13.8">
       <c r="A113" s="22" t="s">
         <v>394</v>
       </c>
@@ -28827,7 +28827,7 @@
       <c r="M113" s="49"/>
       <c r="N113" s="73"/>
     </row>
-    <row r="114" spans="1:14" ht="12.75">
+    <row r="114" spans="1:14" ht="13.8">
       <c r="A114" s="22" t="s">
         <v>395</v>
       </c>
@@ -28865,7 +28865,7 @@
       <c r="M114" s="49"/>
       <c r="N114" s="73"/>
     </row>
-    <row r="115" spans="1:14" ht="12.75">
+    <row r="115" spans="1:14" ht="13.8">
       <c r="A115" s="22" t="s">
         <v>396</v>
       </c>
@@ -28903,7 +28903,7 @@
       <c r="M115" s="49"/>
       <c r="N115" s="73"/>
     </row>
-    <row r="116" spans="1:14" ht="12.75">
+    <row r="116" spans="1:14" ht="13.8">
       <c r="A116" s="22" t="s">
         <v>397</v>
       </c>
@@ -28941,7 +28941,7 @@
       <c r="M116" s="49"/>
       <c r="N116" s="73"/>
     </row>
-    <row r="117" spans="1:14" ht="12.75">
+    <row r="117" spans="1:14" ht="13.8">
       <c r="A117" s="22" t="s">
         <v>398</v>
       </c>
@@ -28979,7 +28979,7 @@
       <c r="M117" s="49"/>
       <c r="N117" s="73"/>
     </row>
-    <row r="118" spans="1:14" ht="12.75">
+    <row r="118" spans="1:14" ht="13.8">
       <c r="A118" s="22" t="s">
         <v>399</v>
       </c>
@@ -29017,7 +29017,7 @@
       <c r="M118" s="49"/>
       <c r="N118" s="73"/>
     </row>
-    <row r="119" spans="1:14" ht="12.75">
+    <row r="119" spans="1:14" ht="13.8">
       <c r="A119" s="22" t="s">
         <v>400</v>
       </c>
@@ -29055,7 +29055,7 @@
       <c r="M119" s="49"/>
       <c r="N119" s="73"/>
     </row>
-    <row r="120" spans="1:14" ht="12.75">
+    <row r="120" spans="1:14" ht="13.8">
       <c r="A120" s="22" t="s">
         <v>401</v>
       </c>
@@ -29093,7 +29093,7 @@
       <c r="M120" s="49"/>
       <c r="N120" s="73"/>
     </row>
-    <row r="121" spans="1:14" ht="12.75">
+    <row r="121" spans="1:14" ht="13.8">
       <c r="A121" s="22" t="s">
         <v>220</v>
       </c>
@@ -29131,7 +29131,7 @@
       <c r="M121" s="49"/>
       <c r="N121" s="73"/>
     </row>
-    <row r="122" spans="1:14" ht="12.75">
+    <row r="122" spans="1:14" ht="13.8">
       <c r="A122" s="20" t="s">
         <v>46</v>
       </c>
@@ -29169,7 +29169,7 @@
       <c r="M122" s="49"/>
       <c r="N122" s="73"/>
     </row>
-    <row r="123" spans="1:14" ht="12.75">
+    <row r="123" spans="1:14" ht="13.8">
       <c r="B123" s="49"/>
       <c r="C123" s="49"/>
       <c r="D123" s="49"/>
@@ -29179,11 +29179,11 @@
       <c r="J123" s="37"/>
       <c r="L123" s="49"/>
     </row>
-    <row r="124" spans="1:14" ht="12.75">
+    <row r="124" spans="1:14" ht="13.8">
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="1:14" ht="12.75">
+    <row r="125" spans="1:14" ht="13.8">
       <c r="A125" s="2" t="s">
         <v>152</v>
       </c>
@@ -29195,7 +29195,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" spans="1:14" ht="12.75">
+    <row r="126" spans="1:14" ht="13.8">
       <c r="A126" s="9" t="s">
         <v>251</v>
       </c>
@@ -29207,7 +29207,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="1:14" ht="38.25">
+    <row r="127" spans="1:14" ht="41.4">
       <c r="A127" s="26" t="s">
         <v>154</v>
       </c>
@@ -29242,7 +29242,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="12.75">
+    <row r="128" spans="1:14" ht="13.8">
       <c r="A128" s="13" t="s">
         <v>155</v>
       </c>
@@ -29278,7 +29278,7 @@
         <v>1526612</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="12.75">
+    <row r="129" spans="1:12" ht="13.8">
       <c r="A129" s="16" t="s">
         <v>156</v>
       </c>
@@ -29314,7 +29314,7 @@
         <v>1535783</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="12.75">
+    <row r="130" spans="1:12" ht="13.8">
       <c r="A130" s="16" t="s">
         <v>157</v>
       </c>
@@ -29350,7 +29350,7 @@
         <v>1062154</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="12.75">
+    <row r="131" spans="1:12" ht="13.8">
       <c r="A131" s="18" t="s">
         <v>158</v>
       </c>
@@ -29386,31 +29386,31 @@
         <v>41.57812259761733</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="12.75">
+    <row r="133" spans="1:12" ht="13.8">
       <c r="B133" s="24"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
     </row>
-    <row r="134" spans="1:12" ht="12.75">
+    <row r="134" spans="1:12" ht="13.8">
       <c r="B134" s="45"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
     </row>
-    <row r="135" spans="1:12" ht="12.75">
+    <row r="135" spans="1:12" ht="13.8">
       <c r="B135" s="45"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
     </row>
-    <row r="136" spans="1:12" ht="12.75">
+    <row r="136" spans="1:12" ht="13.8">
       <c r="B136" s="45"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
     </row>
-    <row r="137" spans="1:12" ht="12.75">
+    <row r="137" spans="1:12" ht="13.8">
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -29424,20 +29424,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="3" customWidth="1"/>
-    <col min="2" max="4" width="12.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="12.85546875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="10.85546875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="3" customWidth="1"/>
-    <col min="13" max="57" width="15.7109375" style="3" customWidth="1"/>
-    <col min="58" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
+    <col min="2" max="4" width="12.88671875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="6" customWidth="1"/>
+    <col min="7" max="9" width="12.88671875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="10.88671875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" style="3" customWidth="1"/>
+    <col min="13" max="57" width="15.6640625" style="3" customWidth="1"/>
+    <col min="58" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75">
+    <row r="1" spans="1:11" ht="18">
       <c r="A1" s="1" t="s">
         <v>137</v>
       </c>
@@ -31209,7 +31209,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="14.25">
+    <row r="83" spans="1:11" ht="16.2">
       <c r="A83" s="8" t="s">
         <v>145</v>
       </c>
@@ -31798,7 +31798,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14.25">
+    <row r="106" spans="1:11" ht="16.2">
       <c r="A106" s="8" t="s">
         <v>145</v>
       </c>
@@ -32369,23 +32369,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J176"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="3" customWidth="1"/>
-    <col min="2" max="4" width="12.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="12.85546875" style="3" customWidth="1"/>
-    <col min="10" max="36" width="15.7109375" style="3" customWidth="1"/>
-    <col min="37" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
+    <col min="2" max="4" width="12.88671875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="6" customWidth="1"/>
+    <col min="7" max="9" width="12.88671875" style="3" customWidth="1"/>
+    <col min="10" max="36" width="15.6640625" style="3" customWidth="1"/>
+    <col min="37" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75">
+    <row r="2" spans="1:10" ht="18">
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:10">
@@ -32410,7 +32410,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="14.25">
+    <row r="5" spans="1:10" ht="16.2">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -32613,7 +32613,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.25">
+    <row r="15" spans="1:10" ht="16.2">
       <c r="A15" s="8" t="s">
         <v>50</v>
       </c>
@@ -33095,7 +33095,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25">
+    <row r="38" spans="1:10" ht="16.2">
       <c r="A38" s="8" t="s">
         <v>52</v>
       </c>
@@ -33294,7 +33294,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25">
+    <row r="48" spans="1:10" ht="16.2">
       <c r="A48" s="8" t="s">
         <v>145</v>
       </c>
@@ -33857,7 +33857,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15">
+    <row r="72" spans="1:10" ht="16.2">
       <c r="A72" s="8" t="s">
         <v>145</v>
       </c>
@@ -34442,7 +34442,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15">
+    <row r="96" spans="1:10" ht="16.2">
       <c r="A96" s="8" t="s">
         <v>145</v>
       </c>
@@ -35006,20 +35006,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="3" customWidth="1"/>
-    <col min="2" max="4" width="12.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="12.85546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
+    <col min="2" max="4" width="12.88671875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="6" customWidth="1"/>
+    <col min="7" max="9" width="12.88671875" style="3" customWidth="1"/>
     <col min="10" max="10" width="16" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" style="3" customWidth="1"/>
-    <col min="12" max="49" width="15.7109375" style="3" customWidth="1"/>
-    <col min="50" max="16384" width="33.140625" style="3"/>
+    <col min="11" max="11" width="25.33203125" style="3" customWidth="1"/>
+    <col min="12" max="49" width="15.6640625" style="3" customWidth="1"/>
+    <col min="50" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
@@ -37582,20 +37582,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AH866"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="31.140625" style="3" customWidth="1"/>
-    <col min="2" max="5" width="12.85546875" style="6" customWidth="1"/>
-    <col min="6" max="16" width="12.85546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="31.140625" style="3" customWidth="1"/>
-    <col min="19" max="33" width="12.85546875" style="3" customWidth="1"/>
-    <col min="34" max="35" width="5.42578125" style="3" customWidth="1"/>
-    <col min="36" max="54" width="15.7109375" style="3" customWidth="1"/>
-    <col min="55" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="31.109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="12.88671875" style="6" customWidth="1"/>
+    <col min="6" max="16" width="12.88671875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="31.109375" style="3" customWidth="1"/>
+    <col min="19" max="33" width="12.88671875" style="3" customWidth="1"/>
+    <col min="34" max="35" width="5.44140625" style="3" customWidth="1"/>
+    <col min="36" max="54" width="15.6640625" style="3" customWidth="1"/>
+    <col min="55" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75">
+    <row r="1" spans="1:31" ht="18">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
@@ -37917,7 +37917,7 @@
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
     </row>
-    <row r="25" spans="1:34" ht="51">
+    <row r="25" spans="1:34" ht="55.2">
       <c r="A25" s="26" t="s">
         <v>50</v>
       </c>
@@ -38489,7 +38489,7 @@
       <c r="V33" s="6"/>
       <c r="W33" s="6"/>
     </row>
-    <row r="34" spans="1:34" ht="51">
+    <row r="34" spans="1:34" ht="55.2">
       <c r="A34" s="15" t="s">
         <v>51</v>
       </c>
@@ -39561,7 +39561,7 @@
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
     </row>
-    <row r="48" spans="1:34" ht="51">
+    <row r="48" spans="1:34" ht="55.2">
       <c r="A48" s="15" t="s">
         <v>145</v>
       </c>
@@ -41583,7 +41583,7 @@
       <c r="V73" s="12"/>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="1:34" ht="14.25">
+    <row r="74" spans="1:34" ht="15.6">
       <c r="A74" s="33" t="s">
         <v>453</v>
       </c>
@@ -41884,7 +41884,7 @@
       <c r="V90" s="6"/>
       <c r="W90" s="6"/>
     </row>
-    <row r="91" spans="1:34" ht="51">
+    <row r="91" spans="1:34" ht="55.2">
       <c r="A91" s="26" t="s">
         <v>50</v>
       </c>
@@ -42456,7 +42456,7 @@
       <c r="V99" s="6"/>
       <c r="W99" s="6"/>
     </row>
-    <row r="100" spans="1:34" ht="51">
+    <row r="100" spans="1:34" ht="55.2">
       <c r="A100" s="15" t="s">
         <v>51</v>
       </c>
@@ -43528,7 +43528,7 @@
       <c r="V113" s="6"/>
       <c r="W113" s="6"/>
     </row>
-    <row r="114" spans="1:34" ht="51">
+    <row r="114" spans="1:34" ht="55.2">
       <c r="A114" s="15" t="s">
         <v>145</v>
       </c>
@@ -45561,19 +45561,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AH872"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" style="3" customWidth="1"/>
-    <col min="2" max="5" width="12.85546875" style="6" customWidth="1"/>
-    <col min="6" max="16" width="12.85546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="31.140625" style="3" customWidth="1"/>
-    <col min="19" max="33" width="12.85546875" style="3" customWidth="1"/>
-    <col min="34" max="51" width="15.7109375" style="3" customWidth="1"/>
-    <col min="52" max="16384" width="33.140625" style="3"/>
+    <col min="1" max="1" width="43.5546875" style="3" customWidth="1"/>
+    <col min="2" max="5" width="12.88671875" style="6" customWidth="1"/>
+    <col min="6" max="16" width="12.88671875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="31.109375" style="3" customWidth="1"/>
+    <col min="19" max="33" width="12.88671875" style="3" customWidth="1"/>
+    <col min="34" max="51" width="15.6640625" style="3" customWidth="1"/>
+    <col min="52" max="16384" width="33.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>141</v>
       </c>
@@ -45595,7 +45595,7 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="14.25">
+    <row r="5" spans="1:5" ht="16.2">
       <c r="A5" s="8" t="s">
         <v>144</v>
       </c>
@@ -45638,7 +45638,7 @@
         <v>1008247.5979317999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="33" t="s">
         <v>640</v>
       </c>
@@ -45849,7 +45849,7 @@
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
     </row>
-    <row r="25" spans="1:34" ht="14.25">
+    <row r="25" spans="1:34" ht="16.2">
       <c r="A25" s="7" t="s">
         <v>342</v>
       </c>
@@ -45861,7 +45861,7 @@
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
     </row>
-    <row r="26" spans="1:34" ht="51">
+    <row r="26" spans="1:34" ht="55.2">
       <c r="A26" s="26" t="s">
         <v>50</v>
       </c>
@@ -46463,7 +46463,7 @@
       <c r="W34" s="6"/>
       <c r="AH34" s="37"/>
     </row>
-    <row r="35" spans="1:34" ht="14.25">
+    <row r="35" spans="1:34" ht="16.2">
       <c r="A35" s="7" t="s">
         <v>343</v>
       </c>
@@ -46479,7 +46479,7 @@
       <c r="W35" s="6"/>
       <c r="AH35" s="37"/>
     </row>
-    <row r="36" spans="1:34" ht="51">
+    <row r="36" spans="1:34" ht="55.2">
       <c r="A36" s="15" t="s">
         <v>51</v>
       </c>
@@ -47592,7 +47592,7 @@
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
     </row>
-    <row r="50" spans="1:34" ht="14.25">
+    <row r="50" spans="1:34" ht="16.2">
       <c r="A50" s="7" t="s">
         <v>344</v>
       </c>
@@ -47606,7 +47606,7 @@
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
     </row>
-    <row r="51" spans="1:34" ht="51">
+    <row r="51" spans="1:34" ht="55.2">
       <c r="A51" s="15" t="s">
         <v>145</v>
       </c>
@@ -49576,7 +49576,7 @@
       <c r="V73" s="6"/>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="1:34" ht="14.25">
+    <row r="74" spans="1:34" ht="16.2">
       <c r="A74" s="8" t="s">
         <v>144</v>
       </c>
@@ -49639,7 +49639,7 @@
       <c r="V76" s="12"/>
       <c r="W76" s="6"/>
     </row>
-    <row r="77" spans="1:34" ht="14.25">
+    <row r="77" spans="1:34" ht="15.6">
       <c r="A77" s="33" t="s">
         <v>455</v>
       </c>
@@ -49939,7 +49939,7 @@
       <c r="V93" s="6"/>
       <c r="W93" s="6"/>
     </row>
-    <row r="94" spans="1:34" ht="14.25">
+    <row r="94" spans="1:34" ht="16.2">
       <c r="A94" s="7" t="s">
         <v>346</v>
       </c>
@@ -49953,7 +49953,7 @@
       <c r="V94" s="6"/>
       <c r="W94" s="6"/>
     </row>
-    <row r="95" spans="1:34" ht="51">
+    <row r="95" spans="1:34" ht="55.2">
       <c r="A95" s="26" t="s">
         <v>50</v>
       </c>
@@ -50550,7 +50550,7 @@
       <c r="W103" s="6"/>
       <c r="AH103" s="37"/>
     </row>
-    <row r="104" spans="1:34" ht="14.25">
+    <row r="104" spans="1:34" ht="16.2">
       <c r="A104" s="7" t="s">
         <v>347</v>
       </c>
@@ -50565,7 +50565,7 @@
       <c r="W104" s="6"/>
       <c r="AH104" s="37"/>
     </row>
-    <row r="105" spans="1:34" ht="51">
+    <row r="105" spans="1:34" ht="55.2">
       <c r="A105" s="15" t="s">
         <v>51</v>
       </c>
@@ -51659,7 +51659,7 @@
       <c r="V118" s="6"/>
       <c r="W118" s="6"/>
     </row>
-    <row r="119" spans="1:34" ht="14.25">
+    <row r="119" spans="1:34" ht="16.2">
       <c r="A119" s="7" t="s">
         <v>348</v>
       </c>
@@ -51673,7 +51673,7 @@
       <c r="V119" s="6"/>
       <c r="W119" s="6"/>
     </row>
-    <row r="120" spans="1:34" ht="51">
+    <row r="120" spans="1:34" ht="55.2">
       <c r="A120" s="15" t="s">
         <v>145</v>
       </c>
